--- a/WHO_AWARE_EML_cat.xlsx
+++ b/WHO_AWARE_EML_cat.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/liley/Documents/Smith/Special Study w: Rob/IQVIA21_SQL/IQVIA21_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADF62B4-6484-5B48-B836-4A825AEF32D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F0257CC-2CFD-1E49-A4D2-0821EE953ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="500" yWindow="740" windowWidth="26860" windowHeight="16220" xr2:uid="{0AE38697-1826-3D40-944D-CEEE2805A602}"/>
+    <workbookView xWindow="500" yWindow="740" windowWidth="25400" windowHeight="16800" xr2:uid="{0AE38697-1826-3D40-944D-CEEE2805A602}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$269</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2644" uniqueCount="632">
   <si>
     <t>Antibiotic</t>
   </si>
@@ -1823,6 +1824,132 @@
   </si>
   <si>
     <t>Beta-lactam/beta-lactamase-inhibitor</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWARE_Cat2019</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Status_EML2019</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Category </t>
+  </si>
+  <si>
+    <t>Listed on EML 2019</t>
+  </si>
+  <si>
+    <t>J01GB06</t>
+  </si>
+  <si>
+    <t>to be assigned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J01FF01 </t>
+  </si>
+  <si>
+    <t>J01RA04</t>
+  </si>
+  <si>
+    <t>Amoxicillin/clavulanic Acid</t>
+  </si>
+  <si>
+    <t>Benzathine benzylpenicillin</t>
+  </si>
+  <si>
+    <t>Cefcapene pivoxil</t>
+  </si>
+  <si>
+    <t>Cefditoren pivoxil</t>
+  </si>
+  <si>
+    <t>Cefetamet pivoxil</t>
+  </si>
+  <si>
+    <t>Cefotiam hexetil</t>
+  </si>
+  <si>
+    <t>Cefpodoxime proxetil</t>
+  </si>
+  <si>
+    <t>Ceftaroline fosamil</t>
+  </si>
+  <si>
+    <t>Ceftazidime-avibactam</t>
+  </si>
+  <si>
+    <t>Cefteram pivoxil</t>
+  </si>
+  <si>
+    <t>Ceftobiprole medocaril</t>
+  </si>
+  <si>
+    <t>Ceftolozane-tazobactam</t>
+  </si>
+  <si>
+    <t>Colistin</t>
+  </si>
+  <si>
+    <t>Dalfopristin-quinupristin</t>
+  </si>
+  <si>
+    <t>Fosfomycin (IV)</t>
+  </si>
+  <si>
+    <t>Fosfomycin (oral)</t>
+  </si>
+  <si>
+    <t>Fusidic Acid</t>
+  </si>
+  <si>
+    <t>Kanamycin</t>
+  </si>
+  <si>
+    <t>Meropenem-vaborbactam</t>
+  </si>
+  <si>
+    <t>Metronidazole (IV)</t>
+  </si>
+  <si>
+    <t>Metronidazole (oral)</t>
+  </si>
+  <si>
+    <t>Minocycline (IV)</t>
+  </si>
+  <si>
+    <t>Minocycline (oral)</t>
+  </si>
+  <si>
+    <t>Neomycin</t>
+  </si>
+  <si>
+    <t>Polymyxin B</t>
+  </si>
+  <si>
+    <t>Procaine benzylpenicillin</t>
+  </si>
+  <si>
+    <t>Rifamycin</t>
+  </si>
+  <si>
+    <t>Spiramycin/metronidazole</t>
+  </si>
+  <si>
+    <t>Streptomycin</t>
+  </si>
+  <si>
+    <t>Sulfamethizole/trimethoprim</t>
+  </si>
+  <si>
+    <t>Vancomycin (IV)</t>
+  </si>
+  <si>
+    <t>Vancomycin (oral)</t>
+  </si>
+  <si>
+    <t>Tetracycline</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1830,7 +1957,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1876,6 +2003,27 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1917,7 +2065,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1926,6 +2074,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2261,8 +2414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01B4EF34-B812-F449-B6D3-408FB8983246}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:H269"/>
+  <dimension ref="A1:J269"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
@@ -2270,11 +2422,11 @@
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="6" width="32.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.85546875" customWidth="1"/>
-    <col min="8" max="8" width="22.42578125" customWidth="1"/>
+    <col min="7" max="9" width="18.85546875" customWidth="1"/>
+    <col min="10" max="10" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2296,11 +2448,17 @@
       <c r="G1" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1">
+    <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2322,11 +2480,19 @@
       <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="str">
+        <f>VLOOKUP(C2,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I2" t="str">
+        <f>VLOOKUP(C2,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J2" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -2348,11 +2514,19 @@
       <c r="G3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" t="str">
+        <f>VLOOKUP(C3,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I3" t="str">
+        <f>VLOOKUP(C3,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J3" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2374,11 +2548,19 @@
       <c r="G4" t="s">
         <v>6</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="str">
+        <f>VLOOKUP(C4,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I4" t="str">
+        <f>VLOOKUP(C4,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J4" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -2400,11 +2582,19 @@
       <c r="G5" t="e">
         <v>#N/A</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="str">
+        <f>VLOOKUP(C5,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I5" t="str">
+        <f>VLOOKUP(C5,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J5" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -2426,11 +2616,19 @@
       <c r="G6" t="s">
         <v>6</v>
       </c>
-      <c r="H6" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="H6" t="str">
+        <f>VLOOKUP(C6,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I6" t="str">
+        <f>VLOOKUP(C6,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J6" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -2452,11 +2650,19 @@
       <c r="G7" t="s">
         <v>14</v>
       </c>
-      <c r="H7" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" t="str">
+        <f>VLOOKUP(C7,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I7" t="str">
+        <f>VLOOKUP(C7,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J7" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -2479,10 +2685,18 @@
         <v>#N/A</v>
       </c>
       <c r="H8" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <f>VLOOKUP(C8,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I8" t="e">
+        <f>VLOOKUP(C8,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J8" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -2505,10 +2719,18 @@
         <v>14</v>
       </c>
       <c r="H9" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <f>VLOOKUP(C9,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I9" t="e">
+        <f>VLOOKUP(C9,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J9" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -2530,11 +2752,19 @@
       <c r="G10" t="s">
         <v>14</v>
       </c>
-      <c r="H10" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" hidden="1">
+      <c r="H10" t="str">
+        <f>VLOOKUP(C10,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I10" t="str">
+        <f>VLOOKUP(C10,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J10" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
         <v>45</v>
       </c>
@@ -2556,11 +2786,19 @@
       <c r="G11" t="s">
         <v>6</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" t="str">
+        <f>VLOOKUP(C11,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I11" t="str">
+        <f>VLOOKUP(C11,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J11" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
         <v>47</v>
       </c>
@@ -2583,10 +2821,18 @@
         <v>#N/A</v>
       </c>
       <c r="H12" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" hidden="1">
+        <f>VLOOKUP(C12,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I12" t="e">
+        <f>VLOOKUP(C12,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J12" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>49</v>
       </c>
@@ -2608,11 +2854,19 @@
       <c r="G13" t="s">
         <v>6</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="str">
+        <f>VLOOKUP(C13,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I13" t="str">
+        <f>VLOOKUP(C13,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J13" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -2635,10 +2889,18 @@
         <v>14</v>
       </c>
       <c r="H14" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <f>VLOOKUP(C14,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I14" t="e">
+        <f>VLOOKUP(C14,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J14" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
         <v>63</v>
       </c>
@@ -2660,11 +2922,19 @@
       <c r="G15" t="s">
         <v>14</v>
       </c>
-      <c r="H15" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="H15" t="str">
+        <f>VLOOKUP(C15,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I15" t="str">
+        <f>VLOOKUP(C15,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J15" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>69</v>
       </c>
@@ -2686,11 +2956,19 @@
       <c r="G16" t="s">
         <v>14</v>
       </c>
-      <c r="H16" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" hidden="1">
+      <c r="H16" t="str">
+        <f>VLOOKUP(C16,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I16" t="str">
+        <f>VLOOKUP(C16,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J16" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
         <v>71</v>
       </c>
@@ -2712,11 +2990,19 @@
       <c r="G17" t="s">
         <v>6</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" t="str">
+        <f>VLOOKUP(C17,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I17" t="str">
+        <f>VLOOKUP(C17,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J17" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
         <v>73</v>
       </c>
@@ -2739,10 +3025,18 @@
         <v>14</v>
       </c>
       <c r="H18" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <f>VLOOKUP(C18,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I18" t="e">
+        <f>VLOOKUP(C18,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
         <v>75</v>
       </c>
@@ -2764,11 +3058,19 @@
       <c r="G19" t="s">
         <v>14</v>
       </c>
-      <c r="H19" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="H19" t="str">
+        <f>VLOOKUP(C19,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I19" t="str">
+        <f>VLOOKUP(C19,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
         <v>79</v>
       </c>
@@ -2790,11 +3092,19 @@
       <c r="G20" t="s">
         <v>14</v>
       </c>
-      <c r="H20" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="H20" t="str">
+        <f>VLOOKUP(C20,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I20" t="str">
+        <f>VLOOKUP(C20,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J20" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
         <v>81</v>
       </c>
@@ -2816,11 +3126,19 @@
       <c r="G21" t="s">
         <v>14</v>
       </c>
-      <c r="H21" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="H21" t="str">
+        <f>VLOOKUP(C21,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I21" t="str">
+        <f>VLOOKUP(C21,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J21" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
         <v>83</v>
       </c>
@@ -2842,11 +3160,19 @@
       <c r="G22" t="s">
         <v>14</v>
       </c>
-      <c r="H22" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1">
+      <c r="H22" t="str">
+        <f>VLOOKUP(C22,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I22" t="str">
+        <f>VLOOKUP(C22,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J22" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
         <v>85</v>
       </c>
@@ -2868,11 +3194,19 @@
       <c r="G23" t="s">
         <v>6</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="str">
+        <f>VLOOKUP(C23,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I23" t="str">
+        <f>VLOOKUP(C23,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J23" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
         <v>140</v>
       </c>
@@ -2894,11 +3228,19 @@
       <c r="G24" t="s">
         <v>14</v>
       </c>
-      <c r="H24" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="H24" t="str">
+        <f>VLOOKUP(C24,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I24" t="str">
+        <f>VLOOKUP(C24,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J24" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
         <v>142</v>
       </c>
@@ -2920,11 +3262,19 @@
       <c r="G25" t="s">
         <v>14</v>
       </c>
-      <c r="H25" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="H25" t="str">
+        <f>VLOOKUP(C25,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I25" t="str">
+        <f>VLOOKUP(C25,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J25" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
         <v>155</v>
       </c>
@@ -2946,11 +3296,19 @@
       <c r="G26" t="s">
         <v>14</v>
       </c>
-      <c r="H26" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" hidden="1">
+      <c r="H26" t="str">
+        <f>VLOOKUP(C26,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I26" t="str">
+        <f>VLOOKUP(C26,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J26" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
         <v>169</v>
       </c>
@@ -2972,11 +3330,19 @@
       <c r="G27" t="s">
         <v>6</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" t="str">
+        <f>VLOOKUP(C27,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I27" t="str">
+        <f>VLOOKUP(C27,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J27" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1">
+    <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
         <v>183</v>
       </c>
@@ -2998,11 +3364,19 @@
       <c r="G28" t="s">
         <v>6</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" t="e">
+        <f>VLOOKUP(C28,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I28" t="e">
+        <f>VLOOKUP(C28,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J28" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
         <v>189</v>
       </c>
@@ -3024,11 +3398,19 @@
       <c r="G29" t="s">
         <v>14</v>
       </c>
-      <c r="H29" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" hidden="1">
+      <c r="H29" t="str">
+        <f>VLOOKUP(C29,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I29" t="str">
+        <f>VLOOKUP(C29,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
         <v>193</v>
       </c>
@@ -3050,11 +3432,19 @@
       <c r="G30" t="s">
         <v>6</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" t="str">
+        <f>VLOOKUP(C30,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I30" t="str">
+        <f>VLOOKUP(C30,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J30" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
         <v>215</v>
       </c>
@@ -3076,11 +3466,19 @@
       <c r="G31" t="s">
         <v>14</v>
       </c>
-      <c r="H31" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" hidden="1">
+      <c r="H31" t="str">
+        <f>VLOOKUP(C31,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I31" t="str">
+        <f>VLOOKUP(C31,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
         <v>221</v>
       </c>
@@ -3102,11 +3500,19 @@
       <c r="G32" t="s">
         <v>6</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" t="str">
+        <f>VLOOKUP(C32,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I32" t="str">
+        <f>VLOOKUP(C32,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J32" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
         <v>225</v>
       </c>
@@ -3129,10 +3535,18 @@
         <v>14</v>
       </c>
       <c r="H33" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <f>VLOOKUP(C33,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I33" t="e">
+        <f>VLOOKUP(C33,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J33" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
         <v>242</v>
       </c>
@@ -3154,11 +3568,19 @@
       <c r="G34" t="s">
         <v>14</v>
       </c>
-      <c r="H34" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="H34" t="str">
+        <f>VLOOKUP(C34,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I34" t="str">
+        <f>VLOOKUP(C34,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J34" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
         <v>252</v>
       </c>
@@ -3181,10 +3603,18 @@
         <v>14</v>
       </c>
       <c r="H35" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" hidden="1">
+        <f>VLOOKUP(C35,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I35" t="e">
+        <f>VLOOKUP(C35,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J35" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
         <v>264</v>
       </c>
@@ -3206,11 +3636,19 @@
       <c r="G36" t="s">
         <v>6</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" t="str">
+        <f>VLOOKUP(C36,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I36" t="str">
+        <f>VLOOKUP(C36,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J36" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
         <v>271</v>
       </c>
@@ -3233,10 +3671,18 @@
         <v>14</v>
       </c>
       <c r="H37" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <f>VLOOKUP(C37,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I37" t="e">
+        <f>VLOOKUP(C37,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J37" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
         <v>309</v>
       </c>
@@ -3258,11 +3704,19 @@
       <c r="G38" t="s">
         <v>14</v>
       </c>
-      <c r="H38" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="H38" t="str">
+        <f>VLOOKUP(C38,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I38" t="str">
+        <f>VLOOKUP(C38,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J38" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
         <v>317</v>
       </c>
@@ -3285,10 +3739,18 @@
         <v>14</v>
       </c>
       <c r="H39" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <f>VLOOKUP(C39,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I39" t="e">
+        <f>VLOOKUP(C39,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J39" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
         <v>319</v>
       </c>
@@ -3311,10 +3773,18 @@
         <v>14</v>
       </c>
       <c r="H40" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <f>VLOOKUP(C40,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I40" t="e">
+        <f>VLOOKUP(C40,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J40" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
         <v>321</v>
       </c>
@@ -3336,11 +3806,19 @@
       <c r="G41" t="s">
         <v>6</v>
       </c>
-      <c r="H41" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1">
+      <c r="H41" t="str">
+        <f>VLOOKUP(C41,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I41" t="str">
+        <f>VLOOKUP(C41,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J41" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
         <v>323</v>
       </c>
@@ -3362,11 +3840,19 @@
       <c r="G42" t="s">
         <v>6</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" t="str">
+        <f>VLOOKUP(C42,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I42" t="str">
+        <f>VLOOKUP(C42,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J42" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
         <v>337</v>
       </c>
@@ -3388,11 +3874,19 @@
       <c r="G43" t="s">
         <v>14</v>
       </c>
-      <c r="H43" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="H43" t="str">
+        <f>VLOOKUP(C43,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I43" t="str">
+        <f>VLOOKUP(C43,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J43" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
         <v>349</v>
       </c>
@@ -3415,10 +3909,18 @@
         <v>14</v>
       </c>
       <c r="H44" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <f>VLOOKUP(C44,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I44" t="e">
+        <f>VLOOKUP(C44,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J44" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
         <v>351</v>
       </c>
@@ -3441,10 +3943,18 @@
         <v>#N/A</v>
       </c>
       <c r="H45" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" hidden="1">
+        <f>VLOOKUP(C45,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I45" t="e">
+        <f>VLOOKUP(C45,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J45" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="2" t="s">
         <v>353</v>
       </c>
@@ -3466,11 +3976,19 @@
       <c r="G46" t="s">
         <v>6</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" t="str">
+        <f>VLOOKUP(C46,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I46" t="str">
+        <f>VLOOKUP(C46,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J46" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
         <v>365</v>
       </c>
@@ -3493,10 +4011,18 @@
         <v>14</v>
       </c>
       <c r="H47" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <f>VLOOKUP(C47,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I47" t="e">
+        <f>VLOOKUP(C47,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J47" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
         <v>367</v>
       </c>
@@ -3519,10 +4045,18 @@
         <v>14</v>
       </c>
       <c r="H48" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <f>VLOOKUP(C48,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I48" t="e">
+        <f>VLOOKUP(C48,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J48" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
         <v>369</v>
       </c>
@@ -3544,11 +4078,19 @@
       <c r="G49" t="s">
         <v>14</v>
       </c>
-      <c r="H49" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="H49" t="str">
+        <f>VLOOKUP(C49,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I49" t="str">
+        <f>VLOOKUP(C49,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J49" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
         <v>383</v>
       </c>
@@ -3570,11 +4112,19 @@
       <c r="G50" t="s">
         <v>14</v>
       </c>
-      <c r="H50" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" hidden="1">
+      <c r="H50" t="str">
+        <f>VLOOKUP(C50,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I50" t="str">
+        <f>VLOOKUP(C50,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J50" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>389</v>
       </c>
@@ -3596,11 +4146,19 @@
       <c r="G51" t="s">
         <v>6</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" t="str">
+        <f>VLOOKUP(C51,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I51" t="str">
+        <f>VLOOKUP(C51,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J51" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
         <v>400</v>
       </c>
@@ -3622,11 +4180,19 @@
       <c r="G52" t="s">
         <v>14</v>
       </c>
-      <c r="H52" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="H52" t="str">
+        <f>VLOOKUP(C52,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I52" t="str">
+        <f>VLOOKUP(C52,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J52" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
         <v>402</v>
       </c>
@@ -3648,11 +4214,19 @@
       <c r="G53" t="s">
         <v>14</v>
       </c>
-      <c r="H53" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" hidden="1">
+      <c r="H53" t="str">
+        <f>VLOOKUP(C53,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I53" t="str">
+        <f>VLOOKUP(C53,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J53" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
         <v>412</v>
       </c>
@@ -3674,11 +4248,19 @@
       <c r="G54" t="s">
         <v>6</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" t="str">
+        <f>VLOOKUP(C54,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I54" t="str">
+        <f>VLOOKUP(C54,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J54" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
         <v>414</v>
       </c>
@@ -3701,10 +4283,18 @@
         <v>#N/A</v>
       </c>
       <c r="H55" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <f>VLOOKUP(C55,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I55" t="e">
+        <f>VLOOKUP(C55,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J55" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
         <v>416</v>
       </c>
@@ -3727,10 +4317,18 @@
         <v>14</v>
       </c>
       <c r="H56" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <f>VLOOKUP(C56,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I56" t="e">
+        <f>VLOOKUP(C56,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J56" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
         <v>445</v>
       </c>
@@ -3753,10 +4351,18 @@
         <v>#N/A</v>
       </c>
       <c r="H57" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <f>VLOOKUP(C57,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I57" t="e">
+        <f>VLOOKUP(C57,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J57" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
         <v>447</v>
       </c>
@@ -3779,10 +4385,18 @@
         <v>14</v>
       </c>
       <c r="H58" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" hidden="1">
+        <f>VLOOKUP(C58,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I58" t="e">
+        <f>VLOOKUP(C58,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J58" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
         <v>457</v>
       </c>
@@ -3804,11 +4418,19 @@
       <c r="G59" t="s">
         <v>6</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" t="str">
+        <f>VLOOKUP(C59,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I59" t="str">
+        <f>VLOOKUP(C59,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J59" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:10">
       <c r="A60" s="2" t="s">
         <v>468</v>
       </c>
@@ -3831,10 +4453,18 @@
         <v>14</v>
       </c>
       <c r="H60" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <f>VLOOKUP(C60,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I60" t="e">
+        <f>VLOOKUP(C60,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J60" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61" s="2" t="s">
         <v>473</v>
       </c>
@@ -3857,10 +4487,18 @@
         <v>#N/A</v>
       </c>
       <c r="H61" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <f>VLOOKUP(C61,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I61" t="e">
+        <f>VLOOKUP(C61,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J61" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62" s="2" t="s">
         <v>476</v>
       </c>
@@ -3883,10 +4521,18 @@
         <v>14</v>
       </c>
       <c r="H62" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <f>VLOOKUP(C62,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I62" t="e">
+        <f>VLOOKUP(C62,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J62" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63" s="2" t="s">
         <v>479</v>
       </c>
@@ -3908,11 +4554,19 @@
       <c r="G63" t="s">
         <v>14</v>
       </c>
-      <c r="H63" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="H63" t="str">
+        <f>VLOOKUP(C63,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I63" t="str">
+        <f>VLOOKUP(C63,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J63" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64" s="2" t="s">
         <v>481</v>
       </c>
@@ -3935,10 +4589,18 @@
         <v>14</v>
       </c>
       <c r="H64" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <f>VLOOKUP(C64,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I64" t="e">
+        <f>VLOOKUP(C64,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J64" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
       <c r="A65" s="2" t="s">
         <v>483</v>
       </c>
@@ -3961,10 +4623,18 @@
         <v>14</v>
       </c>
       <c r="H65" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <f>VLOOKUP(C65,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I65" t="e">
+        <f>VLOOKUP(C65,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J65" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66" s="2" t="s">
         <v>485</v>
       </c>
@@ -3987,10 +4657,18 @@
         <v>14</v>
       </c>
       <c r="H66" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <f>VLOOKUP(C66,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I66" t="e">
+        <f>VLOOKUP(C66,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J66" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67" s="2" t="s">
         <v>487</v>
       </c>
@@ -4013,10 +4691,18 @@
         <v>14</v>
       </c>
       <c r="H67" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
+        <f>VLOOKUP(C67,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I67" t="e">
+        <f>VLOOKUP(C67,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J67" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68" s="2" t="s">
         <v>489</v>
       </c>
@@ -4039,10 +4725,18 @@
         <v>14</v>
       </c>
       <c r="H68" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
+        <f>VLOOKUP(C68,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I68" t="e">
+        <f>VLOOKUP(C68,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J68" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69" s="2" t="s">
         <v>491</v>
       </c>
@@ -4065,10 +4759,18 @@
         <v>14</v>
       </c>
       <c r="H69" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <f>VLOOKUP(C69,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I69" t="e">
+        <f>VLOOKUP(C69,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J69" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70" s="2" t="s">
         <v>493</v>
       </c>
@@ -4091,10 +4793,18 @@
         <v>14</v>
       </c>
       <c r="H70" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <f>VLOOKUP(C70,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I70" t="e">
+        <f>VLOOKUP(C70,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J70" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71" s="2" t="s">
         <v>495</v>
       </c>
@@ -4117,10 +4827,18 @@
         <v>14</v>
       </c>
       <c r="H71" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <f>VLOOKUP(C71,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I71" t="e">
+        <f>VLOOKUP(C71,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J71" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72" s="2" t="s">
         <v>497</v>
       </c>
@@ -4143,10 +4861,18 @@
         <v>14</v>
       </c>
       <c r="H72" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <f>VLOOKUP(C72,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I72" t="e">
+        <f>VLOOKUP(C72,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J72" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73" s="2" t="s">
         <v>499</v>
       </c>
@@ -4168,11 +4894,19 @@
       <c r="G73" t="s">
         <v>14</v>
       </c>
-      <c r="H73" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="H73" t="str">
+        <f>VLOOKUP(C73,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I73" t="str">
+        <f>VLOOKUP(C73,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J73" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74" s="2" t="s">
         <v>501</v>
       </c>
@@ -4195,10 +4929,18 @@
         <v>#N/A</v>
       </c>
       <c r="H74" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" hidden="1">
+        <f>VLOOKUP(C74,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I74" t="e">
+        <f>VLOOKUP(C74,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J74" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75" s="2" t="s">
         <v>503</v>
       </c>
@@ -4220,11 +4962,19 @@
       <c r="G75" t="s">
         <v>6</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" t="str">
+        <f>VLOOKUP(C75,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I75" t="str">
+        <f>VLOOKUP(C75,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J75" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:10">
       <c r="A76" s="2" t="s">
         <v>505</v>
       </c>
@@ -4247,10 +4997,18 @@
         <v>14</v>
       </c>
       <c r="H76" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <f>VLOOKUP(C76,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I76" t="e">
+        <f>VLOOKUP(C76,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J76" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77" s="2" t="s">
         <v>507</v>
       </c>
@@ -4273,10 +5031,18 @@
         <v>14</v>
       </c>
       <c r="H77" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
+        <f>VLOOKUP(C77,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I77" t="e">
+        <f>VLOOKUP(C77,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J77" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78" s="2" t="s">
         <v>509</v>
       </c>
@@ -4299,10 +5065,18 @@
         <v>14</v>
       </c>
       <c r="H78" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+        <f>VLOOKUP(C78,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I78" t="e">
+        <f>VLOOKUP(C78,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J78" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
       <c r="A79" s="2" t="s">
         <v>511</v>
       </c>
@@ -4324,11 +5098,19 @@
       <c r="G79" t="s">
         <v>14</v>
       </c>
-      <c r="H79" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8">
+      <c r="H79" t="str">
+        <f>VLOOKUP(C79,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I79" t="str">
+        <f>VLOOKUP(C79,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J79" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80" s="2" t="s">
         <v>513</v>
       </c>
@@ -4351,10 +5133,18 @@
         <v>#N/A</v>
       </c>
       <c r="H80" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8">
+        <f>VLOOKUP(C80,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I80" t="e">
+        <f>VLOOKUP(C80,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J80" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="2" t="s">
         <v>515</v>
       </c>
@@ -4376,11 +5166,19 @@
       <c r="G81" t="s">
         <v>14</v>
       </c>
-      <c r="H81" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+      <c r="H81" t="str">
+        <f>VLOOKUP(C81,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I81" t="str">
+        <f>VLOOKUP(C81,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J81" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="2" t="s">
         <v>517</v>
       </c>
@@ -4403,10 +5201,18 @@
         <v>14</v>
       </c>
       <c r="H82" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
+        <f>VLOOKUP(C82,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I82" t="e">
+        <f>VLOOKUP(C82,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J82" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83" s="2" t="s">
         <v>519</v>
       </c>
@@ -4429,10 +5235,18 @@
         <v>14</v>
       </c>
       <c r="H83" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+        <f>VLOOKUP(C83,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I83" t="e">
+        <f>VLOOKUP(C83,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J83" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84" s="2" t="s">
         <v>521</v>
       </c>
@@ -4455,10 +5269,18 @@
         <v>14</v>
       </c>
       <c r="H84" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
+        <f>VLOOKUP(C84,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I84" t="e">
+        <f>VLOOKUP(C84,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J84" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85" s="2" t="s">
         <v>523</v>
       </c>
@@ -4481,10 +5303,18 @@
         <v>14</v>
       </c>
       <c r="H85" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
+        <f>VLOOKUP(C85,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I85" t="e">
+        <f>VLOOKUP(C85,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J85" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="2" t="s">
         <v>525</v>
       </c>
@@ -4507,10 +5337,18 @@
         <v>14</v>
       </c>
       <c r="H86" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+        <f>VLOOKUP(C86,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I86" t="e">
+        <f>VLOOKUP(C86,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J86" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="2" t="s">
         <v>527</v>
       </c>
@@ -4533,10 +5371,18 @@
         <v>14</v>
       </c>
       <c r="H87" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
+        <f>VLOOKUP(C87,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I87" t="e">
+        <f>VLOOKUP(C87,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J87" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="2" t="s">
         <v>529</v>
       </c>
@@ -4558,11 +5404,19 @@
       <c r="G88" t="s">
         <v>14</v>
       </c>
-      <c r="H88" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+      <c r="H88" t="str">
+        <f>VLOOKUP(C88,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I88" t="str">
+        <f>VLOOKUP(C88,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J88" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="2" t="s">
         <v>531</v>
       </c>
@@ -4585,12 +5439,20 @@
         <v>14</v>
       </c>
       <c r="H89" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" hidden="1">
+        <f>VLOOKUP(C89,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I89" t="e">
+        <f>VLOOKUP(C89,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J89" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90" s="2" t="s">
-        <v>549</v>
+        <v>631</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>173</v>
@@ -4610,11 +5472,19 @@
       <c r="G90" t="s">
         <v>14</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" t="str">
+        <f>VLOOKUP(C90,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I90" t="str">
+        <f>VLOOKUP(C90,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J90" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:10">
       <c r="A91" s="2" t="s">
         <v>551</v>
       </c>
@@ -4636,11 +5506,19 @@
       <c r="G91" t="s">
         <v>14</v>
       </c>
-      <c r="H91" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
+      <c r="H91" t="str">
+        <f>VLOOKUP(C91,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I91" t="str">
+        <f>VLOOKUP(C91,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J91" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="2" t="s">
         <v>559</v>
       </c>
@@ -4663,10 +5541,18 @@
         <v>14</v>
       </c>
       <c r="H92" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
+        <f>VLOOKUP(C92,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I92" t="e">
+        <f>VLOOKUP(C92,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J92" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
       <c r="A93" s="2" t="s">
         <v>561</v>
       </c>
@@ -4689,10 +5575,18 @@
         <v>14</v>
       </c>
       <c r="H93" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" hidden="1">
+        <f>VLOOKUP(C93,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I93" t="e">
+        <f>VLOOKUP(C93,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J93" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
       <c r="A94" s="2" t="s">
         <v>567</v>
       </c>
@@ -4714,11 +5608,19 @@
       <c r="G94" t="s">
         <v>6</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" t="str">
+        <f>VLOOKUP(C94,Sheet2!A:D,3,0)</f>
+        <v>Access</v>
+      </c>
+      <c r="I94" t="str">
+        <f>VLOOKUP(C94,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J94" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1">
+    <row r="95" spans="1:10">
       <c r="A95" s="2" t="s">
         <v>34</v>
       </c>
@@ -4740,11 +5642,19 @@
       <c r="G95" t="s">
         <v>14</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" t="str">
+        <f>VLOOKUP(C95,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I95" t="str">
+        <f>VLOOKUP(C95,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J95" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:10">
       <c r="A96" s="2" t="s">
         <v>38</v>
       </c>
@@ -4767,10 +5677,18 @@
         <v>#N/A</v>
       </c>
       <c r="H96" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <f>VLOOKUP(C96,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I96" t="e">
+        <f>VLOOKUP(C96,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J96" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97" s="2" t="s">
         <v>61</v>
       </c>
@@ -4793,10 +5711,18 @@
         <v>14</v>
       </c>
       <c r="H97" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" hidden="1">
+        <f>VLOOKUP(C97,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I97" t="e">
+        <f>VLOOKUP(C97,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J97" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98" s="2" t="s">
         <v>101</v>
       </c>
@@ -4818,11 +5744,19 @@
       <c r="G98" t="s">
         <v>6</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" t="e">
+        <f>VLOOKUP(C98,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I98" t="e">
+        <f>VLOOKUP(C98,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J98" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:10">
       <c r="A99" s="2" t="s">
         <v>146</v>
       </c>
@@ -4844,11 +5778,19 @@
       <c r="G99" t="s">
         <v>14</v>
       </c>
-      <c r="H99" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
+      <c r="H99" t="str">
+        <f>VLOOKUP(C99,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I99" t="str">
+        <f>VLOOKUP(C99,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J99" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" s="2" t="s">
         <v>151</v>
       </c>
@@ -4870,11 +5812,19 @@
       <c r="G100" t="s">
         <v>6</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" t="str">
+        <f>VLOOKUP(C100,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I100" t="str">
+        <f>VLOOKUP(C100,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J100" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:10">
       <c r="A101" s="2" t="s">
         <v>161</v>
       </c>
@@ -4896,11 +5846,19 @@
       <c r="G101" t="s">
         <v>14</v>
       </c>
-      <c r="H101" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
+      <c r="H101" t="str">
+        <f>VLOOKUP(C101,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I101" t="str">
+        <f>VLOOKUP(C101,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J101" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="2" t="s">
         <v>163</v>
       </c>
@@ -4922,11 +5880,19 @@
       <c r="G102" t="s">
         <v>14</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" t="str">
+        <f>VLOOKUP(C102,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I102" t="str">
+        <f>VLOOKUP(C102,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J102" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1">
+    <row r="103" spans="1:10">
       <c r="A103" s="2" t="s">
         <v>195</v>
       </c>
@@ -4948,11 +5914,19 @@
       <c r="G103" t="s">
         <v>6</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" t="str">
+        <f>VLOOKUP(C103,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I103" t="str">
+        <f>VLOOKUP(C103,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J103" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:10">
       <c r="A104" s="2" t="s">
         <v>198</v>
       </c>
@@ -4975,10 +5949,18 @@
         <v>14</v>
       </c>
       <c r="H104" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
+        <f>VLOOKUP(C104,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I104" t="e">
+        <f>VLOOKUP(C104,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J104" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10">
       <c r="A105" s="2" t="s">
         <v>200</v>
       </c>
@@ -5000,11 +5982,19 @@
       <c r="G105" t="s">
         <v>14</v>
       </c>
-      <c r="H105" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+      <c r="H105" t="str">
+        <f>VLOOKUP(C105,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I105" t="str">
+        <f>VLOOKUP(C105,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J105" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10">
       <c r="A106" s="2" t="s">
         <v>203</v>
       </c>
@@ -5026,11 +6016,19 @@
       <c r="G106" t="s">
         <v>14</v>
       </c>
-      <c r="H106" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" hidden="1">
+      <c r="H106" t="str">
+        <f>VLOOKUP(C106,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I106" t="str">
+        <f>VLOOKUP(C106,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J106" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10">
       <c r="A107" s="2" t="s">
         <v>206</v>
       </c>
@@ -5052,11 +6050,19 @@
       <c r="G107" t="s">
         <v>14</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" t="str">
+        <f>VLOOKUP(C107,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I107" t="str">
+        <f>VLOOKUP(C107,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J107" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1">
+    <row r="108" spans="1:10">
       <c r="A108" s="2" t="s">
         <v>227</v>
       </c>
@@ -5078,11 +6084,19 @@
       <c r="G108" t="s">
         <v>14</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" t="str">
+        <f>VLOOKUP(C108,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I108" t="str">
+        <f>VLOOKUP(C108,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J108" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:10">
       <c r="A109" s="2" t="s">
         <v>233</v>
       </c>
@@ -5104,11 +6118,19 @@
       <c r="G109" t="s">
         <v>14</v>
       </c>
-      <c r="H109" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" hidden="1">
+      <c r="H109" t="str">
+        <f>VLOOKUP(C109,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I109" t="str">
+        <f>VLOOKUP(C109,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J109" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10">
       <c r="A110" s="2" t="s">
         <v>248</v>
       </c>
@@ -5130,11 +6152,19 @@
       <c r="G110" t="s">
         <v>6</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" t="str">
+        <f>VLOOKUP(C110,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I110" t="str">
+        <f>VLOOKUP(C110,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J110" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:10">
       <c r="A111" s="2" t="s">
         <v>273</v>
       </c>
@@ -5157,10 +6187,18 @@
         <v>14</v>
       </c>
       <c r="H111" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" hidden="1">
+        <f>VLOOKUP(C111,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I111" t="e">
+        <f>VLOOKUP(C111,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J111" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10">
       <c r="A112" s="2" t="s">
         <v>277</v>
       </c>
@@ -5182,11 +6220,19 @@
       <c r="G112" t="s">
         <v>14</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" t="e">
+        <f>VLOOKUP(C112,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I112" t="e">
+        <f>VLOOKUP(C112,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J112" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:10">
       <c r="A113" s="2" t="s">
         <v>291</v>
       </c>
@@ -5209,10 +6255,18 @@
         <v>14</v>
       </c>
       <c r="H113" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" hidden="1">
+        <f>VLOOKUP(C113,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I113" t="e">
+        <f>VLOOKUP(C113,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J113" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10">
       <c r="A114" s="2" t="s">
         <v>300</v>
       </c>
@@ -5234,11 +6288,19 @@
       <c r="G114" t="s">
         <v>6</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" t="str">
+        <f>VLOOKUP(C114,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I114" t="str">
+        <f>VLOOKUP(C114,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J114" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1">
+    <row r="115" spans="1:10">
       <c r="A115" s="2" t="s">
         <v>313</v>
       </c>
@@ -5260,11 +6322,19 @@
       <c r="G115" t="s">
         <v>6</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" t="str">
+        <f>VLOOKUP(C115,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I115" t="str">
+        <f>VLOOKUP(C115,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J115" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:10">
       <c r="A116" s="2" t="s">
         <v>330</v>
       </c>
@@ -5286,11 +6356,19 @@
       <c r="G116" t="s">
         <v>14</v>
       </c>
-      <c r="H116" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" hidden="1">
+      <c r="H116" t="str">
+        <f>VLOOKUP(C116,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I116" t="str">
+        <f>VLOOKUP(C116,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J116" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10">
       <c r="A117" s="2" t="s">
         <v>361</v>
       </c>
@@ -5312,11 +6390,19 @@
       <c r="G117" t="s">
         <v>14</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" t="e">
+        <f>VLOOKUP(C117,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I117" t="e">
+        <f>VLOOKUP(C117,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J117" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:10">
       <c r="A118" s="2" t="s">
         <v>363</v>
       </c>
@@ -5338,11 +6424,19 @@
       <c r="G118" t="s">
         <v>14</v>
       </c>
-      <c r="H118" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" hidden="1">
+      <c r="H118" t="str">
+        <f>VLOOKUP(C118,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I118" t="str">
+        <f>VLOOKUP(C118,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J118" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10">
       <c r="A119" s="2" t="s">
         <v>404</v>
       </c>
@@ -5364,11 +6458,19 @@
       <c r="G119" t="s">
         <v>6</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" t="e">
+        <f>VLOOKUP(C119,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I119" t="e">
+        <f>VLOOKUP(C119,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J119" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1">
+    <row r="120" spans="1:10">
       <c r="A120" s="2" t="s">
         <v>406</v>
       </c>
@@ -5390,11 +6492,19 @@
       <c r="G120" t="s">
         <v>6</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" t="str">
+        <f>VLOOKUP(C120,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I120" t="str">
+        <f>VLOOKUP(C120,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J120" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:10">
       <c r="A121" s="2" t="s">
         <v>408</v>
       </c>
@@ -5417,10 +6527,18 @@
         <v>14</v>
       </c>
       <c r="H121" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
+        <f>VLOOKUP(C121,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I121" t="e">
+        <f>VLOOKUP(C121,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J121" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10">
       <c r="A122" s="2" t="s">
         <v>537</v>
       </c>
@@ -5442,11 +6560,19 @@
       <c r="G122" t="s">
         <v>14</v>
       </c>
-      <c r="H122" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
+      <c r="H122" t="str">
+        <f>VLOOKUP(C122,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I122" t="str">
+        <f>VLOOKUP(C122,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J122" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10">
       <c r="A123" s="2" t="s">
         <v>541</v>
       </c>
@@ -5468,11 +6594,19 @@
       <c r="G123" t="s">
         <v>14</v>
       </c>
-      <c r="H123" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" hidden="1">
+      <c r="H123" t="str">
+        <f>VLOOKUP(C123,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I123" t="str">
+        <f>VLOOKUP(C123,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J123" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10">
       <c r="A124" s="2" t="s">
         <v>556</v>
       </c>
@@ -5494,11 +6628,19 @@
       <c r="G124" t="s">
         <v>14</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H124" t="str">
+        <f>VLOOKUP(C124,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I124" t="str">
+        <f>VLOOKUP(C124,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J124" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:10">
       <c r="A125" s="2" t="s">
         <v>19</v>
       </c>
@@ -5520,11 +6662,19 @@
       <c r="G125" t="s">
         <v>14</v>
       </c>
-      <c r="H125" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+      <c r="H125" t="str">
+        <f>VLOOKUP(C125,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I125" t="str">
+        <f>VLOOKUP(C125,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J125" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10">
       <c r="A126" s="2" t="s">
         <v>22</v>
       </c>
@@ -5547,10 +6697,18 @@
         <v>14</v>
       </c>
       <c r="H126" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" hidden="1">
+        <f>VLOOKUP(C126,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I126" t="e">
+        <f>VLOOKUP(C126,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J126" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10">
       <c r="A127" s="2" t="s">
         <v>29</v>
       </c>
@@ -5572,11 +6730,19 @@
       <c r="G127" t="s">
         <v>6</v>
       </c>
-      <c r="H127" t="s">
+      <c r="H127" t="str">
+        <f>VLOOKUP(C127,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I127" t="str">
+        <f>VLOOKUP(C127,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J127" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:10">
       <c r="A128" s="2" t="s">
         <v>32</v>
       </c>
@@ -5598,11 +6764,19 @@
       <c r="G128" t="s">
         <v>14</v>
       </c>
-      <c r="H128" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
+      <c r="H128" t="str">
+        <f>VLOOKUP(C128,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I128" t="str">
+        <f>VLOOKUP(C128,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J128" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10">
       <c r="A129" s="2" t="s">
         <v>43</v>
       </c>
@@ -5625,10 +6799,18 @@
         <v>14</v>
       </c>
       <c r="H129" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
+        <f>VLOOKUP(C129,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I129" t="e">
+        <f>VLOOKUP(C129,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J129" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10">
       <c r="A130" s="2" t="s">
         <v>51</v>
       </c>
@@ -5650,11 +6832,19 @@
       <c r="G130" t="s">
         <v>14</v>
       </c>
-      <c r="H130" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
+      <c r="H130" t="str">
+        <f>VLOOKUP(C130,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I130" t="str">
+        <f>VLOOKUP(C130,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J130" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10">
       <c r="A131" s="2" t="s">
         <v>57</v>
       </c>
@@ -5676,11 +6866,19 @@
       <c r="G131" t="s">
         <v>14</v>
       </c>
-      <c r="H131" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
+      <c r="H131" t="str">
+        <f>VLOOKUP(C131,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I131" t="str">
+        <f>VLOOKUP(C131,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J131" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10">
       <c r="A132" s="2" t="s">
         <v>59</v>
       </c>
@@ -5703,10 +6901,18 @@
         <v>14</v>
       </c>
       <c r="H132" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
+        <f>VLOOKUP(C132,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I132" t="e">
+        <f>VLOOKUP(C132,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J132" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10">
       <c r="A133" s="2" t="s">
         <v>66</v>
       </c>
@@ -5728,11 +6934,19 @@
       <c r="G133" t="s">
         <v>14</v>
       </c>
-      <c r="H133" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
+      <c r="H133" t="str">
+        <f>VLOOKUP(C133,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I133" t="str">
+        <f>VLOOKUP(C133,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J133" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10">
       <c r="A134" s="2" t="s">
         <v>77</v>
       </c>
@@ -5754,11 +6968,19 @@
       <c r="G134" t="s">
         <v>14</v>
       </c>
-      <c r="H134" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
+      <c r="H134" t="str">
+        <f>VLOOKUP(C134,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I134" t="str">
+        <f>VLOOKUP(C134,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J134" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10">
       <c r="A135" s="2" t="s">
         <v>87</v>
       </c>
@@ -5780,11 +7002,19 @@
       <c r="G135" t="s">
         <v>14</v>
       </c>
-      <c r="H135" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
+      <c r="H135" t="str">
+        <f>VLOOKUP(C135,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I135" t="str">
+        <f>VLOOKUP(C135,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J135" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10">
       <c r="A136" s="2" t="s">
         <v>89</v>
       </c>
@@ -5806,11 +7036,19 @@
       <c r="G136" t="s">
         <v>14</v>
       </c>
-      <c r="H136" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+      <c r="H136" t="str">
+        <f>VLOOKUP(C136,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I136" t="str">
+        <f>VLOOKUP(C136,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J136" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10">
       <c r="A137" s="2" t="s">
         <v>92</v>
       </c>
@@ -5832,11 +7070,19 @@
       <c r="G137" t="s">
         <v>14</v>
       </c>
-      <c r="H137" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
+      <c r="H137" t="str">
+        <f>VLOOKUP(C137,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I137" t="str">
+        <f>VLOOKUP(C137,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J137" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10">
       <c r="A138" s="2" t="s">
         <v>94</v>
       </c>
@@ -5858,11 +7104,19 @@
       <c r="G138" t="s">
         <v>14</v>
       </c>
-      <c r="H138" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" hidden="1">
+      <c r="H138" t="str">
+        <f>VLOOKUP(C138,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I138" t="str">
+        <f>VLOOKUP(C138,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J138" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10">
       <c r="A139" s="2" t="s">
         <v>96</v>
       </c>
@@ -5884,11 +7138,19 @@
       <c r="G139" t="s">
         <v>14</v>
       </c>
-      <c r="H139" t="s">
+      <c r="H139" t="str">
+        <f>VLOOKUP(C139,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I139" t="str">
+        <f>VLOOKUP(C139,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J139" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:10">
       <c r="A140" s="2" t="s">
         <v>99</v>
       </c>
@@ -5910,11 +7172,19 @@
       <c r="G140" t="s">
         <v>14</v>
       </c>
-      <c r="H140" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" hidden="1">
+      <c r="H140" t="str">
+        <f>VLOOKUP(C140,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I140" t="str">
+        <f>VLOOKUP(C140,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J140" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10">
       <c r="A141" s="2" t="s">
         <v>104</v>
       </c>
@@ -5936,11 +7206,19 @@
       <c r="G141" t="s">
         <v>6</v>
       </c>
-      <c r="H141" t="s">
+      <c r="H141" t="str">
+        <f>VLOOKUP(C141,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I141" t="str">
+        <f>VLOOKUP(C141,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J141" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:10">
       <c r="A142" s="2" t="s">
         <v>106</v>
       </c>
@@ -5962,11 +7240,19 @@
       <c r="G142" t="s">
         <v>14</v>
       </c>
-      <c r="H142" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
+      <c r="H142" t="str">
+        <f>VLOOKUP(C142,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I142" t="str">
+        <f>VLOOKUP(C142,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J142" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10">
       <c r="A143" s="2" t="s">
         <v>108</v>
       </c>
@@ -5988,11 +7274,19 @@
       <c r="G143" t="s">
         <v>14</v>
       </c>
-      <c r="H143" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+      <c r="H143" t="str">
+        <f>VLOOKUP(C143,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I143" t="str">
+        <f>VLOOKUP(C143,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J143" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10">
       <c r="A144" s="2" t="s">
         <v>110</v>
       </c>
@@ -6014,11 +7308,19 @@
       <c r="G144" t="s">
         <v>14</v>
       </c>
-      <c r="H144" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
+      <c r="H144" t="str">
+        <f>VLOOKUP(C144,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I144" t="str">
+        <f>VLOOKUP(C144,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J144" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10">
       <c r="A145" s="2" t="s">
         <v>112</v>
       </c>
@@ -6040,11 +7342,19 @@
       <c r="G145" t="s">
         <v>14</v>
       </c>
-      <c r="H145" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+      <c r="H145" t="str">
+        <f>VLOOKUP(C145,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I145" t="str">
+        <f>VLOOKUP(C145,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J145" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10">
       <c r="A146" s="2" t="s">
         <v>114</v>
       </c>
@@ -6066,11 +7376,19 @@
       <c r="G146" t="s">
         <v>14</v>
       </c>
-      <c r="H146" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
+      <c r="H146" t="str">
+        <f>VLOOKUP(C146,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I146" t="str">
+        <f>VLOOKUP(C146,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J146" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10">
       <c r="A147" s="2" t="s">
         <v>116</v>
       </c>
@@ -6092,11 +7410,19 @@
       <c r="G147" t="s">
         <v>14</v>
       </c>
-      <c r="H147" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
+      <c r="H147" t="str">
+        <f>VLOOKUP(C147,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I147" t="str">
+        <f>VLOOKUP(C147,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J147" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
       <c r="A148" s="2" t="s">
         <v>118</v>
       </c>
@@ -6118,11 +7444,19 @@
       <c r="G148" t="s">
         <v>14</v>
       </c>
-      <c r="H148" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
+      <c r="H148" t="str">
+        <f>VLOOKUP(C148,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I148" t="str">
+        <f>VLOOKUP(C148,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J148" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10">
       <c r="A149" s="2" t="s">
         <v>120</v>
       </c>
@@ -6145,10 +7479,18 @@
         <v>14</v>
       </c>
       <c r="H149" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" hidden="1">
+        <f>VLOOKUP(C149,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I149" t="e">
+        <f>VLOOKUP(C149,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J149" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10">
       <c r="A150" s="2" t="s">
         <v>122</v>
       </c>
@@ -6170,11 +7512,19 @@
       <c r="G150" t="s">
         <v>6</v>
       </c>
-      <c r="H150" t="s">
+      <c r="H150" t="str">
+        <f>VLOOKUP(C150,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I150" t="str">
+        <f>VLOOKUP(C150,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J150" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:10">
       <c r="A151" s="2" t="s">
         <v>124</v>
       </c>
@@ -6196,11 +7546,19 @@
       <c r="G151" t="s">
         <v>14</v>
       </c>
-      <c r="H151" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
+      <c r="H151" t="str">
+        <f>VLOOKUP(C151,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I151" t="str">
+        <f>VLOOKUP(C151,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J151" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
       <c r="A152" s="2" t="s">
         <v>126</v>
       </c>
@@ -6222,11 +7580,19 @@
       <c r="G152" t="s">
         <v>14</v>
       </c>
-      <c r="H152" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
+      <c r="H152" t="str">
+        <f>VLOOKUP(C152,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I152" t="str">
+        <f>VLOOKUP(C152,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J152" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153" s="2" t="s">
         <v>128</v>
       </c>
@@ -6248,11 +7614,19 @@
       <c r="G153" t="s">
         <v>14</v>
       </c>
-      <c r="H153" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
+      <c r="H153" t="str">
+        <f>VLOOKUP(C153,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I153" t="str">
+        <f>VLOOKUP(C153,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J153" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154" s="2" t="s">
         <v>130</v>
       </c>
@@ -6274,11 +7648,19 @@
       <c r="G154" t="s">
         <v>14</v>
       </c>
-      <c r="H154" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+      <c r="H154" t="str">
+        <f>VLOOKUP(C154,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I154" t="str">
+        <f>VLOOKUP(C154,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J154" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155" s="2" t="s">
         <v>132</v>
       </c>
@@ -6300,11 +7682,19 @@
       <c r="G155" t="s">
         <v>14</v>
       </c>
-      <c r="H155" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
+      <c r="H155" t="str">
+        <f>VLOOKUP(C155,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I155" t="str">
+        <f>VLOOKUP(C155,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J155" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" s="2" t="s">
         <v>134</v>
       </c>
@@ -6326,11 +7716,19 @@
       <c r="G156" t="s">
         <v>14</v>
       </c>
-      <c r="H156" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
+      <c r="H156" t="str">
+        <f>VLOOKUP(C156,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I156" t="str">
+        <f>VLOOKUP(C156,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J156" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157" s="2" t="s">
         <v>136</v>
       </c>
@@ -6352,11 +7750,19 @@
       <c r="G157" t="s">
         <v>14</v>
       </c>
-      <c r="H157" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+      <c r="H157" t="str">
+        <f>VLOOKUP(C157,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I157" t="str">
+        <f>VLOOKUP(C157,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J157" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158" s="2" t="s">
         <v>138</v>
       </c>
@@ -6378,11 +7784,19 @@
       <c r="G158" t="s">
         <v>14</v>
       </c>
-      <c r="H158" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
+      <c r="H158" t="str">
+        <f>VLOOKUP(C158,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I158" t="str">
+        <f>VLOOKUP(C158,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J158" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159" s="2" t="s">
         <v>144</v>
       </c>
@@ -6405,10 +7819,18 @@
         <v>14</v>
       </c>
       <c r="H159" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" hidden="1">
+        <f>VLOOKUP(C159,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I159" t="e">
+        <f>VLOOKUP(C159,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J159" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160" s="2" t="s">
         <v>149</v>
       </c>
@@ -6430,11 +7852,19 @@
       <c r="G160" t="s">
         <v>6</v>
       </c>
-      <c r="H160" t="s">
+      <c r="H160" t="str">
+        <f>VLOOKUP(C160,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I160" t="str">
+        <f>VLOOKUP(C160,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J160" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:10">
       <c r="A161" s="2" t="s">
         <v>153</v>
       </c>
@@ -6456,11 +7886,19 @@
       <c r="G161" t="s">
         <v>14</v>
       </c>
-      <c r="H161" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
+      <c r="H161" t="str">
+        <f>VLOOKUP(C161,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I161" t="str">
+        <f>VLOOKUP(C161,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J161" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10">
       <c r="A162" s="2" t="s">
         <v>157</v>
       </c>
@@ -6482,11 +7920,19 @@
       <c r="G162" t="s">
         <v>14</v>
       </c>
-      <c r="H162" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
+      <c r="H162" t="str">
+        <f>VLOOKUP(C162,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I162" t="str">
+        <f>VLOOKUP(C162,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J162" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
       <c r="A163" s="2" t="s">
         <v>159</v>
       </c>
@@ -6508,11 +7954,19 @@
       <c r="G163" t="s">
         <v>14</v>
       </c>
-      <c r="H163" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" hidden="1">
+      <c r="H163" t="str">
+        <f>VLOOKUP(C163,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I163" t="str">
+        <f>VLOOKUP(C163,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J163" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10">
       <c r="A164" s="2" t="s">
         <v>165</v>
       </c>
@@ -6534,11 +7988,19 @@
       <c r="G164" t="s">
         <v>6</v>
       </c>
-      <c r="H164" t="s">
+      <c r="H164" t="str">
+        <f>VLOOKUP(C164,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I164" t="str">
+        <f>VLOOKUP(C164,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J164" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1">
+    <row r="165" spans="1:10">
       <c r="A165" s="2" t="s">
         <v>167</v>
       </c>
@@ -6560,11 +8022,19 @@
       <c r="G165" t="s">
         <v>6</v>
       </c>
-      <c r="H165" t="s">
+      <c r="H165" t="str">
+        <f>VLOOKUP(C165,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I165" t="str">
+        <f>VLOOKUP(C165,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J165" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:10">
       <c r="A166" s="2" t="s">
         <v>172</v>
       </c>
@@ -6586,11 +8056,19 @@
       <c r="G166" t="s">
         <v>14</v>
       </c>
-      <c r="H166" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
+      <c r="H166" t="str">
+        <f>VLOOKUP(C166,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I166" t="str">
+        <f>VLOOKUP(C166,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J166" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10">
       <c r="A167" s="2" t="s">
         <v>175</v>
       </c>
@@ -6613,10 +8091,18 @@
         <v>14</v>
       </c>
       <c r="H167" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" hidden="1">
+        <f>VLOOKUP(C167,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I167" t="e">
+        <f>VLOOKUP(C167,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J167" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10">
       <c r="A168" s="2" t="s">
         <v>178</v>
       </c>
@@ -6638,11 +8124,19 @@
       <c r="G168" t="s">
         <v>6</v>
       </c>
-      <c r="H168" t="s">
+      <c r="H168" t="str">
+        <f>VLOOKUP(C168,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I168" t="str">
+        <f>VLOOKUP(C168,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J168" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1">
+    <row r="169" spans="1:10">
       <c r="A169" s="2" t="s">
         <v>181</v>
       </c>
@@ -6664,11 +8158,19 @@
       <c r="G169" t="s">
         <v>6</v>
       </c>
-      <c r="H169" t="s">
+      <c r="H169" t="str">
+        <f>VLOOKUP(C169,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I169" t="str">
+        <f>VLOOKUP(C169,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J169" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:10">
       <c r="A170" s="2" t="s">
         <v>186</v>
       </c>
@@ -6690,11 +8192,19 @@
       <c r="G170" t="s">
         <v>14</v>
       </c>
-      <c r="H170" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8">
+      <c r="H170" t="str">
+        <f>VLOOKUP(C170,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I170" t="str">
+        <f>VLOOKUP(C170,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J170" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10">
       <c r="A171" s="2" t="s">
         <v>191</v>
       </c>
@@ -6717,10 +8227,18 @@
         <v>14</v>
       </c>
       <c r="H171" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" hidden="1">
+        <f>VLOOKUP(C171,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I171" t="e">
+        <f>VLOOKUP(C171,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J171" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10">
       <c r="A172" s="2" t="s">
         <v>209</v>
       </c>
@@ -6742,11 +8260,19 @@
       <c r="G172" t="s">
         <v>14</v>
       </c>
-      <c r="H172" t="s">
+      <c r="H172" t="str">
+        <f>VLOOKUP(C172,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I172" t="str">
+        <f>VLOOKUP(C172,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J172" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:10">
       <c r="A173" s="2" t="s">
         <v>211</v>
       </c>
@@ -6769,10 +8295,18 @@
         <v>14</v>
       </c>
       <c r="H173" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8">
+        <f>VLOOKUP(C173,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I173" t="e">
+        <f>VLOOKUP(C173,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J173" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10">
       <c r="A174" s="2" t="s">
         <v>213</v>
       </c>
@@ -6794,11 +8328,19 @@
       <c r="G174" t="s">
         <v>14</v>
       </c>
-      <c r="H174" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8">
+      <c r="H174" t="str">
+        <f>VLOOKUP(C174,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I174" t="str">
+        <f>VLOOKUP(C174,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J174" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10">
       <c r="A175" s="2" t="s">
         <v>217</v>
       </c>
@@ -6820,11 +8362,19 @@
       <c r="G175" t="s">
         <v>14</v>
       </c>
-      <c r="H175" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8">
+      <c r="H175" t="str">
+        <f>VLOOKUP(C175,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I175" t="str">
+        <f>VLOOKUP(C175,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J175" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
       <c r="A176" s="2" t="s">
         <v>219</v>
       </c>
@@ -6846,11 +8396,19 @@
       <c r="G176" t="s">
         <v>14</v>
       </c>
-      <c r="H176" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8">
+      <c r="H176" t="str">
+        <f>VLOOKUP(C176,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I176" t="str">
+        <f>VLOOKUP(C176,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J176" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10">
       <c r="A177" s="2" t="s">
         <v>223</v>
       </c>
@@ -6872,11 +8430,19 @@
       <c r="G177" t="s">
         <v>14</v>
       </c>
-      <c r="H177" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8">
+      <c r="H177" t="str">
+        <f>VLOOKUP(C177,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I177" t="str">
+        <f>VLOOKUP(C177,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J177" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10">
       <c r="A178" s="2" t="s">
         <v>229</v>
       </c>
@@ -6898,11 +8464,19 @@
       <c r="G178" t="s">
         <v>14</v>
       </c>
-      <c r="H178" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" hidden="1">
+      <c r="H178" t="str">
+        <f>VLOOKUP(C178,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I178" t="str">
+        <f>VLOOKUP(C178,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J178" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10">
       <c r="A179" s="2" t="s">
         <v>231</v>
       </c>
@@ -6924,11 +8498,19 @@
       <c r="G179" t="s">
         <v>14</v>
       </c>
-      <c r="H179" t="s">
+      <c r="H179" t="str">
+        <f>VLOOKUP(C179,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I179" t="str">
+        <f>VLOOKUP(C179,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J179" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:10">
       <c r="A180" s="2" t="s">
         <v>236</v>
       </c>
@@ -6951,10 +8533,18 @@
         <v>14</v>
       </c>
       <c r="H180" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8">
+        <f>VLOOKUP(C180,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I180" t="e">
+        <f>VLOOKUP(C180,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J180" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10">
       <c r="A181" s="2" t="s">
         <v>238</v>
       </c>
@@ -6976,11 +8566,19 @@
       <c r="G181" t="s">
         <v>14</v>
       </c>
-      <c r="H181" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" hidden="1">
+      <c r="H181" t="str">
+        <f>VLOOKUP(C181,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I181" t="str">
+        <f>VLOOKUP(C181,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J181" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10">
       <c r="A182" s="2" t="s">
         <v>240</v>
       </c>
@@ -7002,11 +8600,19 @@
       <c r="G182" t="s">
         <v>14</v>
       </c>
-      <c r="H182" t="s">
+      <c r="H182" t="str">
+        <f>VLOOKUP(C182,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I182" t="str">
+        <f>VLOOKUP(C182,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J182" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:10">
       <c r="A183" s="2" t="s">
         <v>244</v>
       </c>
@@ -7028,11 +8634,19 @@
       <c r="G183" t="s">
         <v>14</v>
       </c>
-      <c r="H183" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8">
+      <c r="H183" t="str">
+        <f>VLOOKUP(C183,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I183" t="str">
+        <f>VLOOKUP(C183,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J183" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10">
       <c r="A184" s="2" t="s">
         <v>246</v>
       </c>
@@ -7055,10 +8669,18 @@
         <v>14</v>
       </c>
       <c r="H184" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" hidden="1">
+        <f>VLOOKUP(C184,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I184" t="e">
+        <f>VLOOKUP(C184,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J184" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10">
       <c r="A185" s="2" t="s">
         <v>251</v>
       </c>
@@ -7080,11 +8702,19 @@
       <c r="G185" t="s">
         <v>14</v>
       </c>
-      <c r="H185" t="s">
+      <c r="H185" t="str">
+        <f>VLOOKUP(C185,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I185" t="str">
+        <f>VLOOKUP(C185,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J185" t="s">
         <v>586</v>
       </c>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:10">
       <c r="A186" s="2" t="s">
         <v>255</v>
       </c>
@@ -7106,11 +8736,19 @@
       <c r="G186" t="s">
         <v>14</v>
       </c>
-      <c r="H186" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8">
+      <c r="H186" t="str">
+        <f>VLOOKUP(C186,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I186" t="str">
+        <f>VLOOKUP(C186,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J186" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10">
       <c r="A187" s="2" t="s">
         <v>258</v>
       </c>
@@ -7132,11 +8770,19 @@
       <c r="G187" t="s">
         <v>14</v>
       </c>
-      <c r="H187" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" hidden="1">
+      <c r="H187" t="str">
+        <f>VLOOKUP(C187,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I187" t="str">
+        <f>VLOOKUP(C187,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J187" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10">
       <c r="A188" s="2" t="s">
         <v>260</v>
       </c>
@@ -7158,11 +8804,19 @@
       <c r="G188" t="s">
         <v>14</v>
       </c>
-      <c r="H188" t="s">
+      <c r="H188" t="str">
+        <f>VLOOKUP(C188,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I188" t="str">
+        <f>VLOOKUP(C188,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J188" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:10">
       <c r="A189" s="2" t="s">
         <v>262</v>
       </c>
@@ -7184,11 +8838,19 @@
       <c r="G189" t="s">
         <v>14</v>
       </c>
-      <c r="H189" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8">
+      <c r="H189" t="str">
+        <f>VLOOKUP(C189,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I189" t="str">
+        <f>VLOOKUP(C189,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J189" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10">
       <c r="A190" s="2" t="s">
         <v>266</v>
       </c>
@@ -7211,10 +8873,18 @@
         <v>#N/A</v>
       </c>
       <c r="H190" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8">
+        <f>VLOOKUP(C190,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I190" t="e">
+        <f>VLOOKUP(C190,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J190" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10">
       <c r="A191" s="2" t="s">
         <v>269</v>
       </c>
@@ -7237,10 +8907,18 @@
         <v>14</v>
       </c>
       <c r="H191" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" hidden="1">
+        <f>VLOOKUP(C191,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I191" t="e">
+        <f>VLOOKUP(C191,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J191" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="192" spans="1:10">
       <c r="A192" s="2" t="s">
         <v>275</v>
       </c>
@@ -7262,11 +8940,19 @@
       <c r="G192" t="s">
         <v>14</v>
       </c>
-      <c r="H192" t="s">
+      <c r="H192" t="str">
+        <f>VLOOKUP(C192,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I192" t="str">
+        <f>VLOOKUP(C192,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J192" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:10">
       <c r="A193" s="2" t="s">
         <v>279</v>
       </c>
@@ -7288,11 +8974,19 @@
       <c r="G193" t="s">
         <v>14</v>
       </c>
-      <c r="H193" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8">
+      <c r="H193" t="str">
+        <f>VLOOKUP(C193,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I193" t="str">
+        <f>VLOOKUP(C193,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J193" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="194" spans="1:10">
       <c r="A194" s="2" t="s">
         <v>281</v>
       </c>
@@ -7314,11 +9008,19 @@
       <c r="G194" t="s">
         <v>14</v>
       </c>
-      <c r="H194" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" hidden="1">
+      <c r="H194" t="str">
+        <f>VLOOKUP(C194,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I194" t="str">
+        <f>VLOOKUP(C194,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J194" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="195" spans="1:10">
       <c r="A195" s="2" t="s">
         <v>283</v>
       </c>
@@ -7340,11 +9042,19 @@
       <c r="G195" t="s">
         <v>14</v>
       </c>
-      <c r="H195" t="s">
+      <c r="H195" t="str">
+        <f>VLOOKUP(C195,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I195" t="str">
+        <f>VLOOKUP(C195,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J195" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:10">
       <c r="A196" s="2" t="s">
         <v>285</v>
       </c>
@@ -7367,10 +9077,18 @@
         <v>14</v>
       </c>
       <c r="H196" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8">
+        <f>VLOOKUP(C196,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I196" t="e">
+        <f>VLOOKUP(C196,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J196" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="197" spans="1:10">
       <c r="A197" s="2" t="s">
         <v>287</v>
       </c>
@@ -7393,10 +9111,18 @@
         <v>14</v>
       </c>
       <c r="H197" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8">
+        <f>VLOOKUP(C197,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I197" t="e">
+        <f>VLOOKUP(C197,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J197" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="198" spans="1:10">
       <c r="A198" s="2" t="s">
         <v>289</v>
       </c>
@@ -7418,11 +9144,19 @@
       <c r="G198" t="s">
         <v>14</v>
       </c>
-      <c r="H198" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" hidden="1">
+      <c r="H198" t="str">
+        <f>VLOOKUP(C198,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I198" t="str">
+        <f>VLOOKUP(C198,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J198" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="199" spans="1:10">
       <c r="A199" s="2" t="s">
         <v>294</v>
       </c>
@@ -7444,11 +9178,19 @@
       <c r="G199" t="s">
         <v>14</v>
       </c>
-      <c r="H199" t="s">
+      <c r="H199" t="str">
+        <f>VLOOKUP(C199,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I199" t="str">
+        <f>VLOOKUP(C199,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J199" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:10">
       <c r="A200" s="2" t="s">
         <v>296</v>
       </c>
@@ -7471,10 +9213,18 @@
         <v>14</v>
       </c>
       <c r="H200" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8">
+        <f>VLOOKUP(C200,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I200" t="e">
+        <f>VLOOKUP(C200,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J200" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10">
       <c r="A201" s="2" t="s">
         <v>298</v>
       </c>
@@ -7496,11 +9246,19 @@
       <c r="G201" t="s">
         <v>14</v>
       </c>
-      <c r="H201" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8">
+      <c r="H201" t="str">
+        <f>VLOOKUP(C201,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I201" t="str">
+        <f>VLOOKUP(C201,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J201" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="202" spans="1:10">
       <c r="A202" s="2" t="s">
         <v>303</v>
       </c>
@@ -7522,11 +9280,19 @@
       <c r="G202" t="s">
         <v>14</v>
       </c>
-      <c r="H202" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8">
+      <c r="H202" t="str">
+        <f>VLOOKUP(C202,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I202" t="str">
+        <f>VLOOKUP(C202,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J202" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="203" spans="1:10">
       <c r="A203" s="2" t="s">
         <v>305</v>
       </c>
@@ -7549,10 +9315,18 @@
         <v>14</v>
       </c>
       <c r="H203" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8">
+        <f>VLOOKUP(C203,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I203" t="e">
+        <f>VLOOKUP(C203,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J203" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="204" spans="1:10">
       <c r="A204" s="2" t="s">
         <v>307</v>
       </c>
@@ -7574,11 +9348,19 @@
       <c r="G204" t="s">
         <v>14</v>
       </c>
-      <c r="H204" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" hidden="1">
+      <c r="H204" t="str">
+        <f>VLOOKUP(C204,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I204" t="str">
+        <f>VLOOKUP(C204,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J204" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="205" spans="1:10">
       <c r="A205" s="2" t="s">
         <v>311</v>
       </c>
@@ -7600,11 +9382,19 @@
       <c r="G205" t="s">
         <v>6</v>
       </c>
-      <c r="H205" t="s">
+      <c r="H205" t="str">
+        <f>VLOOKUP(C205,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I205" t="str">
+        <f>VLOOKUP(C205,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J205" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:10">
       <c r="A206" s="2" t="s">
         <v>315</v>
       </c>
@@ -7626,11 +9416,19 @@
       <c r="G206" t="s">
         <v>14</v>
       </c>
-      <c r="H206" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8">
+      <c r="H206" t="str">
+        <f>VLOOKUP(C206,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I206" t="str">
+        <f>VLOOKUP(C206,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J206" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="207" spans="1:10">
       <c r="A207" s="2" t="s">
         <v>325</v>
       </c>
@@ -7652,11 +9450,19 @@
       <c r="G207" t="s">
         <v>14</v>
       </c>
-      <c r="H207" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8">
+      <c r="H207" t="str">
+        <f>VLOOKUP(C207,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I207" t="str">
+        <f>VLOOKUP(C207,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J207" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="208" spans="1:10">
       <c r="A208" s="2" t="s">
         <v>327</v>
       </c>
@@ -7679,10 +9485,18 @@
         <v>14</v>
       </c>
       <c r="H208" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8">
+        <f>VLOOKUP(C208,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I208" t="e">
+        <f>VLOOKUP(C208,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J208" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
       <c r="A209" s="2" t="s">
         <v>328</v>
       </c>
@@ -7704,11 +9518,19 @@
       <c r="G209" t="s">
         <v>14</v>
       </c>
-      <c r="H209" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8">
+      <c r="H209" t="str">
+        <f>VLOOKUP(C209,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I209" t="str">
+        <f>VLOOKUP(C209,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J209" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
       <c r="A210" s="2" t="s">
         <v>332</v>
       </c>
@@ -7730,11 +9552,19 @@
       <c r="G210" t="s">
         <v>14</v>
       </c>
-      <c r="H210" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8">
+      <c r="H210" t="str">
+        <f>VLOOKUP(C210,Sheet2!A:D,3,0)</f>
+        <v>Reserve</v>
+      </c>
+      <c r="I210" t="str">
+        <f>VLOOKUP(C210,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J210" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="211" spans="1:10">
       <c r="A211" s="2" t="s">
         <v>333</v>
       </c>
@@ -7757,10 +9587,18 @@
         <v>14</v>
       </c>
       <c r="H211" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" hidden="1">
+        <f>VLOOKUP(C211,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I211" t="e">
+        <f>VLOOKUP(C211,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J211" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="212" spans="1:10">
       <c r="A212" s="2" t="s">
         <v>335</v>
       </c>
@@ -7782,11 +9620,19 @@
       <c r="G212" t="s">
         <v>14</v>
       </c>
-      <c r="H212" t="s">
+      <c r="H212" t="str">
+        <f>VLOOKUP(C212,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I212" t="str">
+        <f>VLOOKUP(C212,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J212" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:10">
       <c r="A213" s="2" t="s">
         <v>339</v>
       </c>
@@ -7809,10 +9655,18 @@
         <v>#N/A</v>
       </c>
       <c r="H213" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8">
+        <f>VLOOKUP(C213,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I213" t="e">
+        <f>VLOOKUP(C213,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J213" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
       <c r="A214" s="2" t="s">
         <v>341</v>
       </c>
@@ -7835,10 +9689,18 @@
         <v>14</v>
       </c>
       <c r="H214" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8">
+        <f>VLOOKUP(C214,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I214" t="e">
+        <f>VLOOKUP(C214,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J214" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
       <c r="A215" s="2" t="s">
         <v>343</v>
       </c>
@@ -7860,11 +9722,19 @@
       <c r="G215" t="s">
         <v>14</v>
       </c>
-      <c r="H215" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8">
+      <c r="H215" t="str">
+        <f>VLOOKUP(C215,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I215" t="str">
+        <f>VLOOKUP(C215,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J215" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="216" spans="1:10">
       <c r="A216" s="2" t="s">
         <v>345</v>
       </c>
@@ -7887,10 +9757,18 @@
         <v>14</v>
       </c>
       <c r="H216" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8">
+        <f>VLOOKUP(C216,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I216" t="e">
+        <f>VLOOKUP(C216,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J216" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="217" spans="1:10">
       <c r="A217" s="2" t="s">
         <v>347</v>
       </c>
@@ -7912,11 +9790,19 @@
       <c r="G217" t="s">
         <v>14</v>
       </c>
-      <c r="H217" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8">
+      <c r="H217" t="str">
+        <f>VLOOKUP(C217,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I217" t="str">
+        <f>VLOOKUP(C217,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J217" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="218" spans="1:10">
       <c r="A218" s="2" t="s">
         <v>355</v>
       </c>
@@ -7938,11 +9824,19 @@
       <c r="G218" t="s">
         <v>14</v>
       </c>
-      <c r="H218" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" hidden="1">
+      <c r="H218" t="str">
+        <f>VLOOKUP(C218,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I218" t="str">
+        <f>VLOOKUP(C218,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J218" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="219" spans="1:10">
       <c r="A219" s="2" t="s">
         <v>357</v>
       </c>
@@ -7964,11 +9858,19 @@
       <c r="G219" t="s">
         <v>14</v>
       </c>
-      <c r="H219" t="s">
+      <c r="H219" t="str">
+        <f>VLOOKUP(C219,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I219" t="str">
+        <f>VLOOKUP(C219,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J219" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:10">
       <c r="A220" s="2" t="s">
         <v>359</v>
       </c>
@@ -7990,11 +9892,19 @@
       <c r="G220" t="s">
         <v>14</v>
       </c>
-      <c r="H220" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8">
+      <c r="H220" t="str">
+        <f>VLOOKUP(C220,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I220" t="str">
+        <f>VLOOKUP(C220,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J220" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10">
       <c r="A221" s="2" t="s">
         <v>371</v>
       </c>
@@ -8017,10 +9927,18 @@
         <v>14</v>
       </c>
       <c r="H221" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8">
+        <f>VLOOKUP(C221,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I221" t="e">
+        <f>VLOOKUP(C221,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J221" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
       <c r="A222" s="2" t="s">
         <v>373</v>
       </c>
@@ -8042,11 +9960,19 @@
       <c r="G222" t="s">
         <v>14</v>
       </c>
-      <c r="H222" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8">
+      <c r="H222" t="str">
+        <f>VLOOKUP(C222,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I222" t="str">
+        <f>VLOOKUP(C222,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J222" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10">
       <c r="A223" s="2" t="s">
         <v>375</v>
       </c>
@@ -8069,10 +9995,18 @@
         <v>14</v>
       </c>
       <c r="H223" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8">
+        <f>VLOOKUP(C223,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I223" t="e">
+        <f>VLOOKUP(C223,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J223" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10">
       <c r="A224" s="2" t="s">
         <v>377</v>
       </c>
@@ -8095,10 +10029,18 @@
         <v>#N/A</v>
       </c>
       <c r="H224" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8">
+        <f>VLOOKUP(C224,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I224" t="e">
+        <f>VLOOKUP(C224,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J224" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10">
       <c r="A225" s="2" t="s">
         <v>379</v>
       </c>
@@ -8120,11 +10062,19 @@
       <c r="G225" t="s">
         <v>14</v>
       </c>
-      <c r="H225" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8">
+      <c r="H225" t="str">
+        <f>VLOOKUP(C225,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I225" t="str">
+        <f>VLOOKUP(C225,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J225" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10">
       <c r="A226" s="2" t="s">
         <v>381</v>
       </c>
@@ -8146,11 +10096,19 @@
       <c r="G226" t="s">
         <v>14</v>
       </c>
-      <c r="H226" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8">
+      <c r="H226" t="str">
+        <f>VLOOKUP(C226,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I226" t="str">
+        <f>VLOOKUP(C226,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J226" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10">
       <c r="A227" s="2" t="s">
         <v>385</v>
       </c>
@@ -8173,10 +10131,18 @@
         <v>14</v>
       </c>
       <c r="H227" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8">
+        <f>VLOOKUP(C227,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I227" t="e">
+        <f>VLOOKUP(C227,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J227" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10">
       <c r="A228" s="2" t="s">
         <v>387</v>
       </c>
@@ -8198,11 +10164,19 @@
       <c r="G228" t="s">
         <v>14</v>
       </c>
-      <c r="H228" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
+      <c r="H228" t="str">
+        <f>VLOOKUP(C228,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I228" t="str">
+        <f>VLOOKUP(C228,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J228" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10">
       <c r="A229" s="2" t="s">
         <v>391</v>
       </c>
@@ -8225,10 +10199,18 @@
         <v>14</v>
       </c>
       <c r="H229" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8">
+        <f>VLOOKUP(C229,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I229" t="e">
+        <f>VLOOKUP(C229,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J229" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10">
       <c r="A230" s="2" t="s">
         <v>393</v>
       </c>
@@ -8250,11 +10232,19 @@
       <c r="G230" t="s">
         <v>14</v>
       </c>
-      <c r="H230" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" hidden="1">
+      <c r="H230" t="str">
+        <f>VLOOKUP(C230,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I230" t="str">
+        <f>VLOOKUP(C230,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J230" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10">
       <c r="A231" s="2" t="s">
         <v>395</v>
       </c>
@@ -8276,11 +10266,19 @@
       <c r="G231" t="s">
         <v>6</v>
       </c>
-      <c r="H231" t="s">
+      <c r="H231" t="str">
+        <f>VLOOKUP(C231,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I231" t="str">
+        <f>VLOOKUP(C231,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J231" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:10">
       <c r="A232" s="2" t="s">
         <v>398</v>
       </c>
@@ -8303,10 +10301,18 @@
         <v>14</v>
       </c>
       <c r="H232" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8">
+        <f>VLOOKUP(C232,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I232" t="e">
+        <f>VLOOKUP(C232,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J232" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10">
       <c r="A233" s="2" t="s">
         <v>410</v>
       </c>
@@ -8328,11 +10334,19 @@
       <c r="G233" t="s">
         <v>14</v>
       </c>
-      <c r="H233" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8">
+      <c r="H233" t="str">
+        <f>VLOOKUP(C233,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I233" t="str">
+        <f>VLOOKUP(C233,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J233" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10">
       <c r="A234" s="2" t="s">
         <v>418</v>
       </c>
@@ -8354,11 +10368,19 @@
       <c r="G234" t="s">
         <v>14</v>
       </c>
-      <c r="H234" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8">
+      <c r="H234" t="str">
+        <f>VLOOKUP(C234,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I234" t="str">
+        <f>VLOOKUP(C234,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J234" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10">
       <c r="A235" s="2" t="s">
         <v>420</v>
       </c>
@@ -8380,11 +10402,19 @@
       <c r="G235" t="s">
         <v>14</v>
       </c>
-      <c r="H235" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" hidden="1">
+      <c r="H235" t="str">
+        <f>VLOOKUP(C235,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I235" t="str">
+        <f>VLOOKUP(C235,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J235" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10">
       <c r="A236" s="2" t="s">
         <v>422</v>
       </c>
@@ -8406,11 +10436,19 @@
       <c r="G236" t="s">
         <v>14</v>
       </c>
-      <c r="H236" t="s">
+      <c r="H236" t="str">
+        <f>VLOOKUP(C236,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I236" t="str">
+        <f>VLOOKUP(C236,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J236" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1">
+    <row r="237" spans="1:10">
       <c r="A237" s="2" t="s">
         <v>425</v>
       </c>
@@ -8432,11 +10470,19 @@
       <c r="G237" t="s">
         <v>14</v>
       </c>
-      <c r="H237" t="s">
+      <c r="H237" t="str">
+        <f>VLOOKUP(C237,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I237" t="str">
+        <f>VLOOKUP(C237,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J237" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:10">
       <c r="A238" s="2" t="s">
         <v>427</v>
       </c>
@@ -8458,11 +10504,19 @@
       <c r="G238" t="s">
         <v>14</v>
       </c>
-      <c r="H238" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8">
+      <c r="H238" t="str">
+        <f>VLOOKUP(C238,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I238" t="str">
+        <f>VLOOKUP(C238,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J238" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10">
       <c r="A239" s="2" t="s">
         <v>429</v>
       </c>
@@ -8485,10 +10539,18 @@
         <v>14</v>
       </c>
       <c r="H239" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8">
+        <f>VLOOKUP(C239,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I239" t="e">
+        <f>VLOOKUP(C239,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J239" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10">
       <c r="A240" s="2" t="s">
         <v>431</v>
       </c>
@@ -8510,11 +10572,19 @@
       <c r="G240" t="s">
         <v>14</v>
       </c>
-      <c r="H240" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8">
+      <c r="H240" t="str">
+        <f>VLOOKUP(C240,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I240" t="str">
+        <f>VLOOKUP(C240,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J240" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10">
       <c r="A241" s="2" t="s">
         <v>433</v>
       </c>
@@ -8537,10 +10607,18 @@
         <v>14</v>
       </c>
       <c r="H241" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8">
+        <f>VLOOKUP(C241,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I241" t="e">
+        <f>VLOOKUP(C241,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J241" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10">
       <c r="A242" s="2" t="s">
         <v>435</v>
       </c>
@@ -8563,10 +10641,18 @@
         <v>14</v>
       </c>
       <c r="H242" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8">
+        <f>VLOOKUP(C242,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I242" t="e">
+        <f>VLOOKUP(C242,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J242" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10">
       <c r="A243" s="2" t="s">
         <v>437</v>
       </c>
@@ -8589,10 +10675,18 @@
         <v>14</v>
       </c>
       <c r="H243" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8">
+        <f>VLOOKUP(C243,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I243" t="e">
+        <f>VLOOKUP(C243,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J243" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10">
       <c r="A244" s="2" t="s">
         <v>439</v>
       </c>
@@ -8614,11 +10708,19 @@
       <c r="G244" t="s">
         <v>14</v>
       </c>
-      <c r="H244" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8">
+      <c r="H244" t="str">
+        <f>VLOOKUP(C244,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I244" t="str">
+        <f>VLOOKUP(C244,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J244" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10">
       <c r="A245" s="2" t="s">
         <v>441</v>
       </c>
@@ -8640,11 +10742,19 @@
       <c r="G245" t="s">
         <v>14</v>
       </c>
-      <c r="H245" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8">
+      <c r="H245" t="str">
+        <f>VLOOKUP(C245,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I245" t="str">
+        <f>VLOOKUP(C245,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J245" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10">
       <c r="A246" s="2" t="s">
         <v>443</v>
       </c>
@@ -8667,10 +10777,18 @@
         <v>14</v>
       </c>
       <c r="H246" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8">
+        <f>VLOOKUP(C246,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I246" t="e">
+        <f>VLOOKUP(C246,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J246" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10">
       <c r="A247" s="2" t="s">
         <v>449</v>
       </c>
@@ -8692,11 +10810,19 @@
       <c r="G247" t="s">
         <v>14</v>
       </c>
-      <c r="H247" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8">
+      <c r="H247" t="str">
+        <f>VLOOKUP(C247,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I247" t="str">
+        <f>VLOOKUP(C247,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J247" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10">
       <c r="A248" s="2" t="s">
         <v>451</v>
       </c>
@@ -8718,11 +10844,19 @@
       <c r="G248" t="s">
         <v>14</v>
       </c>
-      <c r="H248" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8">
+      <c r="H248" t="str">
+        <f>VLOOKUP(C248,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I248" t="str">
+        <f>VLOOKUP(C248,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J248" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10">
       <c r="A249" s="2" t="s">
         <v>453</v>
       </c>
@@ -8745,10 +10879,18 @@
         <v>14</v>
       </c>
       <c r="H249" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8">
+        <f>VLOOKUP(C249,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I249" t="e">
+        <f>VLOOKUP(C249,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J249" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10">
       <c r="A250" s="2" t="s">
         <v>455</v>
       </c>
@@ -8770,11 +10912,19 @@
       <c r="G250" t="s">
         <v>14</v>
       </c>
-      <c r="H250" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8">
+      <c r="H250" t="str">
+        <f>VLOOKUP(C250,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I250" t="str">
+        <f>VLOOKUP(C250,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J250" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10">
       <c r="A251" s="2" t="s">
         <v>460</v>
       </c>
@@ -8796,11 +10946,19 @@
       <c r="G251" t="s">
         <v>14</v>
       </c>
-      <c r="H251" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8">
+      <c r="H251" t="str">
+        <f>VLOOKUP(C251,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I251" t="str">
+        <f>VLOOKUP(C251,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J251" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10">
       <c r="A252" s="2" t="s">
         <v>462</v>
       </c>
@@ -8823,10 +10981,18 @@
         <v>14</v>
       </c>
       <c r="H252" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" hidden="1">
+        <f>VLOOKUP(C252,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I252" t="e">
+        <f>VLOOKUP(C252,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J252" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10">
       <c r="A253" s="2" t="s">
         <v>464</v>
       </c>
@@ -8848,11 +11014,19 @@
       <c r="G253" t="s">
         <v>14</v>
       </c>
-      <c r="H253" t="s">
+      <c r="H253" t="str">
+        <f>VLOOKUP(C253,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I253" t="str">
+        <f>VLOOKUP(C253,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J253" t="s">
         <v>585</v>
       </c>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:10">
       <c r="A254" s="2" t="s">
         <v>466</v>
       </c>
@@ -8875,10 +11049,18 @@
         <v>14</v>
       </c>
       <c r="H254" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8">
+        <f>VLOOKUP(C254,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I254" t="e">
+        <f>VLOOKUP(C254,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J254" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10">
       <c r="A255" s="2" t="s">
         <v>471</v>
       </c>
@@ -8900,11 +11082,19 @@
       <c r="G255" t="s">
         <v>14</v>
       </c>
-      <c r="H255" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8">
+      <c r="H255" t="str">
+        <f>VLOOKUP(C255,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I255" t="str">
+        <f>VLOOKUP(C255,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J255" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10">
       <c r="A256" s="2" t="s">
         <v>533</v>
       </c>
@@ -8927,10 +11117,18 @@
         <v>14</v>
       </c>
       <c r="H256" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8">
+        <f>VLOOKUP(C256,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I256" t="e">
+        <f>VLOOKUP(C256,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J256" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10">
       <c r="A257" s="2" t="s">
         <v>535</v>
       </c>
@@ -8952,11 +11150,19 @@
       <c r="G257" t="s">
         <v>14</v>
       </c>
-      <c r="H257" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8">
+      <c r="H257" t="str">
+        <f>VLOOKUP(C257,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I257" t="str">
+        <f>VLOOKUP(C257,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J257" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10">
       <c r="A258" s="2" t="s">
         <v>539</v>
       </c>
@@ -8978,11 +11184,19 @@
       <c r="G258" t="s">
         <v>14</v>
       </c>
-      <c r="H258" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8">
+      <c r="H258" t="str">
+        <f>VLOOKUP(C258,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I258" t="str">
+        <f>VLOOKUP(C258,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J258" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10">
       <c r="A259" s="2" t="s">
         <v>543</v>
       </c>
@@ -9004,11 +11218,19 @@
       <c r="G259" t="s">
         <v>14</v>
       </c>
-      <c r="H259" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8">
+      <c r="H259" t="str">
+        <f>VLOOKUP(C259,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I259" t="str">
+        <f>VLOOKUP(C259,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J259" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10">
       <c r="A260" s="2" t="s">
         <v>545</v>
       </c>
@@ -9031,10 +11253,18 @@
         <v>14</v>
       </c>
       <c r="H260" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8">
+        <f>VLOOKUP(C260,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I260" t="e">
+        <f>VLOOKUP(C260,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J260" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10">
       <c r="A261" s="2" t="s">
         <v>547</v>
       </c>
@@ -9056,11 +11286,19 @@
       <c r="G261" t="s">
         <v>14</v>
       </c>
-      <c r="H261" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8">
+      <c r="H261" t="str">
+        <f>VLOOKUP(C261,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I261" t="str">
+        <f>VLOOKUP(C261,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J261" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10">
       <c r="A262" s="2" t="s">
         <v>553</v>
       </c>
@@ -9082,11 +11320,19 @@
       <c r="G262" t="s">
         <v>14</v>
       </c>
-      <c r="H262" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8">
+      <c r="H262" t="str">
+        <f>VLOOKUP(C262,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I262" t="str">
+        <f>VLOOKUP(C262,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J262" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10">
       <c r="A263" s="2" t="s">
         <v>555</v>
       </c>
@@ -9109,10 +11355,18 @@
         <v>#N/A</v>
       </c>
       <c r="H263" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8">
+        <f>VLOOKUP(C263,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I263" t="e">
+        <f>VLOOKUP(C263,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J263" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10">
       <c r="A264" s="2" t="s">
         <v>563</v>
       </c>
@@ -9134,11 +11388,19 @@
       <c r="G264" t="s">
         <v>14</v>
       </c>
-      <c r="H264" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8">
+      <c r="H264" t="str">
+        <f>VLOOKUP(C264,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I264" t="str">
+        <f>VLOOKUP(C264,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J264" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10">
       <c r="A265" s="2" t="s">
         <v>565</v>
       </c>
@@ -9160,11 +11422,19 @@
       <c r="G265" t="s">
         <v>14</v>
       </c>
-      <c r="H265" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8">
+      <c r="H265" t="str">
+        <f>VLOOKUP(C265,Sheet2!A:D,3,0)</f>
+        <v>Watch</v>
+      </c>
+      <c r="I265" t="str">
+        <f>VLOOKUP(C265,Sheet2!A:D,4,0)</f>
+        <v>No</v>
+      </c>
+      <c r="J265" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10">
       <c r="A266" s="2" t="s">
         <v>569</v>
       </c>
@@ -9187,10 +11457,18 @@
         <v>14</v>
       </c>
       <c r="H266" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8">
+        <f>VLOOKUP(C266,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I266" t="e">
+        <f>VLOOKUP(C266,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J266" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10">
       <c r="A267" s="2" t="s">
         <v>571</v>
       </c>
@@ -9213,10 +11491,18 @@
         <v>14</v>
       </c>
       <c r="H267" t="e">
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" hidden="1">
+        <f>VLOOKUP(C267,Sheet2!A:D,3,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I267" t="e">
+        <f>VLOOKUP(C267,Sheet2!A:D,4,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="J267" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10">
       <c r="A268" s="2" t="s">
         <v>573</v>
       </c>
@@ -9238,11 +11524,19 @@
       <c r="G268" t="s">
         <v>6</v>
       </c>
-      <c r="H268" t="s">
+      <c r="H268" t="str">
+        <f>VLOOKUP(C268,Sheet2!A:D,3,0)</f>
+        <v xml:space="preserve">Watch </v>
+      </c>
+      <c r="I268" t="str">
+        <f>VLOOKUP(C268,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J268" t="s">
         <v>587</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1">
+    <row r="269" spans="1:10">
       <c r="A269" s="2" t="s">
         <v>575</v>
       </c>
@@ -9264,18 +11558,20 @@
       <c r="G269" t="s">
         <v>6</v>
       </c>
-      <c r="H269" t="s">
+      <c r="H269" t="str">
+        <f>VLOOKUP(C269,Sheet2!A:D,3,0)</f>
+        <v xml:space="preserve">Watch </v>
+      </c>
+      <c r="I269" t="str">
+        <f>VLOOKUP(C269,Sheet2!A:D,4,0)</f>
+        <v>Yes</v>
+      </c>
+      <c r="J269" t="s">
         <v>587</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H269" xr:uid="{01B4EF34-B812-F449-B6D3-408FB8983246}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="#N/A"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J269" xr:uid="{01B4EF34-B812-F449-B6D3-408FB8983246}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E269">
     <sortCondition ref="D2:D269"/>
     <sortCondition ref="A2:A269"/>
@@ -9284,4 +11580,2549 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE27811-9C3C-904C-85FE-7C6BE57BAFB4}">
+  <dimension ref="A1:D181"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>602</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>607</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>611</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C82" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C83" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C90" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>613</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="C94" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="C96" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C98" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C100" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C102" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="C107" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B110" s="10" t="s">
+        <v>617</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C118" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C122" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C124" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="C126" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C132" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C138" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>623</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="C148" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C150" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="C154" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B156" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>460</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D157" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C158" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D158" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C160" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D160" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="B163" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D164" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D165" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D166" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>535</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D167" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="B168" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D168" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>539</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D169" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="B170" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="C170" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D170" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D171" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="C172" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D172" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D174" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D175" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B176" s="10" t="s">
+        <v>556</v>
+      </c>
+      <c r="C176" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D176" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C178" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D178" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D179" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="C180" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D180" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>630</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>